--- a/output/第10期計画_交付金評価指標と全国集計の受領点検.xlsx
+++ b/output/第10期計画_交付金評価指標と全国集計の受領点検.xlsx
@@ -15,6 +15,8 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="05_指標群別の位置" sheetId="6" state="visible" r:id="rId6"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="06_成果指向型配分枠" sheetId="7" state="visible" r:id="rId7"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="07_成果品への反映" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="08_都道府県分の受領点検" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="09_北海道の評価と当広域連合" sheetId="10" state="visible" r:id="rId10"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -614,7 +616,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F27"/>
+  <dimension ref="A1:F29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -635,7 +637,7 @@
     <row r="2" ht="60" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>令和8年9月2日に受領した4ファイル（PDFは同一ファイルの重複のため実体は3種類のエクセルと1種類のPDF）の点検結果です。エクセル3件は既受領資料の原本、PDFは新規です。</t>
+          <t>令和8年9月2日に受領した4ファイル（PDFは同一ファイルの重複のため実体は3種類のエクセルと1種類のPDF）及び令和8年9月25日に受領した都道府県分2ファイルの点検結果です。エクセル3件は既受領資料の原本、PDFは新規です。都道府県分は08・09シートで扱います。</t>
         </is>
       </c>
     </row>
@@ -694,7 +696,7 @@
       </c>
       <c r="D6" s="6" t="inlineStr">
         <is>
-          <t>3町の得点の原本。全国1,745市町村・北海道179市町村の集計値を算出できるようになった。</t>
+          <t>3町の得点の原本。全国1,741市町村・北海道179市町村の集計値を算出できるようになった。</t>
         </is>
       </c>
       <c r="E6" s="6" t="inlineStr">
@@ -798,137 +800,153 @@
         </is>
       </c>
     </row>
-    <row r="11" ht="18" customHeight="1">
-      <c r="A11" s="3" t="inlineStr">
+    <row r="10" ht="64" customHeight="1">
+      <c r="A10" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="B10" s="6" t="inlineStr">
+        <is>
+          <t>001732599.pdf</t>
+        </is>
+      </c>
+      <c r="C10" s="6" t="inlineStr">
+        <is>
+          <t>令和8年度評価指標（都道府県分）（38頁）</t>
+        </is>
+      </c>
+      <c r="D10" s="6" t="inlineStr">
+        <is>
+          <t>都道府県分の評価指標。北海道が管内市町村に対して行う支援の評価の視点が分かる。当広域連合が直接に得点するものではない。</t>
+        </is>
+      </c>
+      <c r="E10" s="6" t="inlineStr">
+        <is>
+          <t>新規（令和8年9月25日受領）</t>
+        </is>
+      </c>
+      <c r="F10" s="8" t="inlineStr">
+        <is>
+          <t>新規</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="64" customHeight="1">
+      <c r="A11" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="B11" s="6" t="inlineStr">
+        <is>
+          <t>001732598.xlsx</t>
+        </is>
+      </c>
+      <c r="C11" s="6" t="inlineStr">
+        <is>
+          <t>令和8年度 全国集計（都道府県）（66行×752列）</t>
+        </is>
+      </c>
+      <c r="D11" s="6" t="inlineStr">
+        <is>
+          <t>47都道府県の得点。北海道550点・全国19位。当広域連合及び3町の得点は載っていない。</t>
+        </is>
+      </c>
+      <c r="E11" s="6" t="inlineStr">
+        <is>
+          <t>新規（令和8年9月25日受領）</t>
+        </is>
+      </c>
+      <c r="F11" s="8" t="inlineStr">
+        <is>
+          <t>新規</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="18" customHeight="1">
+      <c r="A13" s="3" t="inlineStr">
         <is>
           <t>【2　点検の結果】</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="32" customHeight="1">
-      <c r="A12" s="4" t="inlineStr">
+    <row r="14" ht="32" customHeight="1">
+      <c r="A14" s="4" t="inlineStr">
         <is>
           <t>No.</t>
         </is>
       </c>
-      <c r="B12" s="4" t="inlineStr">
+      <c r="B14" s="4" t="inlineStr">
         <is>
           <t>確認した事項</t>
         </is>
       </c>
-      <c r="C12" s="4" t="inlineStr">
+      <c r="C14" s="4" t="inlineStr">
         <is>
           <t>結果</t>
         </is>
       </c>
-      <c r="D12" s="4" t="inlineStr"/>
-      <c r="E12" s="4" t="inlineStr"/>
-      <c r="F12" s="4" t="inlineStr">
+      <c r="D14" s="4" t="inlineStr"/>
+      <c r="E14" s="4" t="inlineStr"/>
+      <c r="F14" s="4" t="inlineStr">
         <is>
           <t>判定</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="76" customHeight="1">
-      <c r="A13" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="B13" s="6" t="inlineStr">
-        <is>
-          <t>収録値との突合</t>
-        </is>
-      </c>
-      <c r="C13" s="6" t="inlineStr">
-        <is>
-          <t>3町×3か年×22項目の198値をすべて突合しました。不一致は0件です。data_kofukin.py の収録値は原本と一致しています。</t>
-        </is>
-      </c>
-      <c r="D13" s="9" t="n"/>
-      <c r="E13" s="10" t="n"/>
-      <c r="F13" s="8" t="inlineStr">
-        <is>
-          <t>一致</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="76" customHeight="1">
-      <c r="A14" s="5" t="n">
-        <v>2</v>
-      </c>
-      <c r="B14" s="6" t="inlineStr">
-        <is>
-          <t>広域連合の行に得点がないことの確認</t>
-        </is>
-      </c>
-      <c r="C14" s="6" t="inlineStr">
-        <is>
-          <t>大雪地区広域連合（保険者番号01832・018325）の行は3か年とも得点欄が空欄で、3町それぞれの行に得点が記載されています。交付金は市町村に交付されるためです。既存の整理と一致します。</t>
-        </is>
-      </c>
-      <c r="D14" s="9" t="n"/>
-      <c r="E14" s="10" t="n"/>
-      <c r="F14" s="8" t="inlineStr">
-        <is>
-          <t>一致</t>
         </is>
       </c>
     </row>
     <row r="15" ht="76" customHeight="1">
       <c r="A15" s="5" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="B15" s="6" t="inlineStr">
         <is>
-          <t>令和8年度の集計に成果指向型配分枠の列がないこと</t>
+          <t>収録値との突合</t>
         </is>
       </c>
       <c r="C15" s="6" t="inlineStr">
         <is>
-          <t>令和8年度評価指標には成果指向型配分枠（100点）がありますが、令和8年度交付金の全国集計には該当する列がありません。値の入る最終列は「今年度順位」（336列目）です。</t>
+          <t>3町×3か年×22項目の198値をすべて突合しました。不一致は0件です。data_kofukin.py の収録値は原本と一致しています。</t>
         </is>
       </c>
       <c r="D15" s="9" t="n"/>
       <c r="E15" s="10" t="n"/>
       <c r="F15" s="8" t="inlineStr">
         <is>
-          <t>確認</t>
+          <t>一致</t>
         </is>
       </c>
     </row>
     <row r="16" ht="76" customHeight="1">
       <c r="A16" s="5" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="B16" s="6" t="inlineStr">
         <is>
-          <t>評価の時点</t>
+          <t>広域連合の行に得点がないことの確認</t>
         </is>
       </c>
       <c r="C16" s="6" t="inlineStr">
         <is>
-          <t>令和8年度評価指標の「時点」欄は「2025年度実施（予定を含む）の状況を評価」です。令和8年度交付金は令和7年度に実施した取組を評価しています。</t>
+          <t>大雪地区広域連合（保険者番号01832・018325）の行は3か年とも得点欄が空欄で、3町それぞれの行に得点が記載されています。交付金は市町村に交付されるためです。既存の整理と一致します。</t>
         </is>
       </c>
       <c r="D16" s="9" t="n"/>
       <c r="E16" s="10" t="n"/>
       <c r="F16" s="8" t="inlineStr">
         <is>
-          <t>確認</t>
+          <t>一致</t>
         </is>
       </c>
     </row>
     <row r="17" ht="76" customHeight="1">
       <c r="A17" s="5" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="B17" s="6" t="inlineStr">
         <is>
-          <t>配点の検証</t>
+          <t>令和8年度の集計に成果指向型配分枠の列がないこと</t>
         </is>
       </c>
       <c r="C17" s="6" t="inlineStr">
         <is>
-          <t>公表資料の明細列を合算した配点（大項目53項目・推進460点・支援469点）は満点ではありません。評価指標による満点は推進400点・支援400点です。差は目標Ⅳ成果指標群（推進・支援とも160→100）と支援目標Ⅰ（ⅱ）活動指標群（57→48）に生じています（03シート）。</t>
+          <t>令和8年度評価指標には成果指向型配分枠（100点）がありますが、令和8年度交付金の全国集計には該当する列がありません。値の入る最終列は「今年度順位」（336列目）です。</t>
         </is>
       </c>
       <c r="D17" s="9" t="n"/>
@@ -939,93 +957,93 @@
         </is>
       </c>
     </row>
-    <row r="19" ht="18" customHeight="1">
-      <c r="A19" s="3" t="inlineStr">
+    <row r="18" ht="76" customHeight="1">
+      <c r="A18" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="B18" s="6" t="inlineStr">
+        <is>
+          <t>評価の時点</t>
+        </is>
+      </c>
+      <c r="C18" s="6" t="inlineStr">
+        <is>
+          <t>令和8年度評価指標の「時点」欄は「2025年度実施（予定を含む）の状況を評価」です。令和8年度交付金は令和7年度に実施した取組を評価しています。</t>
+        </is>
+      </c>
+      <c r="D18" s="9" t="n"/>
+      <c r="E18" s="10" t="n"/>
+      <c r="F18" s="8" t="inlineStr">
+        <is>
+          <t>確認</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="76" customHeight="1">
+      <c r="A19" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="B19" s="6" t="inlineStr">
+        <is>
+          <t>配点の検証</t>
+        </is>
+      </c>
+      <c r="C19" s="6" t="inlineStr">
+        <is>
+          <t>公表資料の明細列を合算した配点（大項目53項目・推進460点・支援469点）は満点ではありません。評価指標による満点は推進400点・支援400点です。差は目標Ⅳ成果指標群（推進・支援とも160→100）と支援目標Ⅰ（ⅱ）活動指標群（57→48）に生じています（03シート）。</t>
+        </is>
+      </c>
+      <c r="D19" s="9" t="n"/>
+      <c r="E19" s="10" t="n"/>
+      <c r="F19" s="8" t="inlineStr">
+        <is>
+          <t>確認</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="18" customHeight="1">
+      <c r="A21" s="3" t="inlineStr">
         <is>
           <t>【3　この受領により新たに分かったこと】</t>
         </is>
       </c>
     </row>
-    <row r="20" ht="32" customHeight="1">
-      <c r="A20" s="4" t="inlineStr">
+    <row r="22" ht="32" customHeight="1">
+      <c r="A22" s="4" t="inlineStr">
         <is>
           <t>No.</t>
         </is>
       </c>
-      <c r="B20" s="4" t="inlineStr">
+      <c r="B22" s="4" t="inlineStr">
         <is>
           <t>事項</t>
         </is>
       </c>
-      <c r="C20" s="4" t="inlineStr">
+      <c r="C22" s="4" t="inlineStr">
         <is>
           <t>内容</t>
         </is>
       </c>
-      <c r="D20" s="4" t="inlineStr"/>
-      <c r="E20" s="4" t="inlineStr"/>
-      <c r="F20" s="4" t="inlineStr">
+      <c r="D22" s="4" t="inlineStr"/>
+      <c r="E22" s="4" t="inlineStr"/>
+      <c r="F22" s="4" t="inlineStr">
         <is>
           <t>重み</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="76" customHeight="1">
-      <c r="A21" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="B21" s="6" t="inlineStr">
-        <is>
-          <t>全国平均が上がる一方で3町は横ばいである</t>
-        </is>
-      </c>
-      <c r="C21" s="6" t="inlineStr">
-        <is>
-          <t>全国平均は令和6年度422.4点から令和8年度454.9点へ32.5点上がりました。3町平均は332.0点から334.0点へ2.0点の変化にとどまります。対全国比は78.6％から73.4％へ低下しています。</t>
-        </is>
-      </c>
-      <c r="D21" s="9" t="n"/>
-      <c r="E21" s="10" t="n"/>
-      <c r="F21" s="11" t="inlineStr">
-        <is>
-          <t>大</t>
-        </is>
-      </c>
-    </row>
-    <row r="22" ht="76" customHeight="1">
-      <c r="A22" s="5" t="n">
-        <v>2</v>
-      </c>
-      <c r="B22" s="6" t="inlineStr">
-        <is>
-          <t>全国の順位が下がり続けている</t>
-        </is>
-      </c>
-      <c r="C22" s="6" t="inlineStr">
-        <is>
-          <t>推進・支援合計の全国順位（下位からの位置）は、東川町が15.0％→6.7％、美瑛町が14.3％→6.0％、東神楽町が28.3％→20.5％です。令和8年度は東川町・美瑛町が全国の下位1割以内に入りました。</t>
-        </is>
-      </c>
-      <c r="D22" s="9" t="n"/>
-      <c r="E22" s="10" t="n"/>
-      <c r="F22" s="11" t="inlineStr">
-        <is>
-          <t>大</t>
         </is>
       </c>
     </row>
     <row r="23" ht="76" customHeight="1">
       <c r="A23" s="5" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="B23" s="6" t="inlineStr">
         <is>
-          <t>成果指標群だけは全国を上回る</t>
+          <t>全国平均が上がる一方で3町は横ばいである</t>
         </is>
       </c>
       <c r="C23" s="6" t="inlineStr">
         <is>
-          <t>令和8年度の目標Ⅳ成果指標群は3町とも55点で、全国平均47.7点・北海道平均54.4点を上回ります。要介護度の変化と認定率という結果は良好である一方、体制・取組と活動の指標が低いという構造です。</t>
+          <t>全国平均は令和6年度422.4点から令和8年度454.9点へ32.5点上がりました。3町平均は332.0点から334.0点へ2.0点の変化にとどまります。対全国比は78.6％から73.4％へ低下しています。</t>
         </is>
       </c>
       <c r="D23" s="9" t="n"/>
@@ -1038,38 +1056,38 @@
     </row>
     <row r="24" ht="76" customHeight="1">
       <c r="A24" s="5" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="B24" s="6" t="inlineStr">
         <is>
-          <t>評価の対象年度が確定した</t>
+          <t>全国の順位が下がり続けている</t>
         </is>
       </c>
       <c r="C24" s="6" t="inlineStr">
         <is>
-          <t>令和8年度交付金は令和7年度に実施した取組を評価しています。第9期（令和6〜8年度）の取組のうち、交付金で外部評価されているのは令和5〜7年度の取組です。令和8年度の取組は令和9年度交付金で評価されるため、第9期の最終年度の取組は本計画の策定時には評価結果が出ません。</t>
+          <t>推進・支援合計の全国順位（下位からの位置）は、東川町が15.0％→6.7％、美瑛町が14.3％→6.0％、東神楽町が28.3％→20.5％です。令和8年度は東川町・美瑛町が全国の下位1割以内に入りました。</t>
         </is>
       </c>
       <c r="D24" s="9" t="n"/>
       <c r="E24" s="10" t="n"/>
-      <c r="F24" s="12" t="inlineStr">
-        <is>
-          <t>中</t>
+      <c r="F24" s="11" t="inlineStr">
+        <is>
+          <t>大</t>
         </is>
       </c>
     </row>
     <row r="25" ht="76" customHeight="1">
       <c r="A25" s="5" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="B25" s="6" t="inlineStr">
         <is>
-          <t>成果指向型配分枠が新設された</t>
+          <t>成果指標群だけは全国を上回る</t>
         </is>
       </c>
       <c r="C25" s="6" t="inlineStr">
         <is>
-          <t>令和8年度から、成果指向型の介護予防・健康づくりの取組を100点満点で評価する枠が新設されました。地域のデータ分析に基づき、対象層・アウトプット指標・アウトカム指標と目標値を設定することが要件です。第10期の施策設計に直接関わります（06シート）。</t>
+          <t>令和8年度の目標Ⅳ成果指標群は3町とも55点で、全国平均47.7点・北海道平均54.4点を上回ります。要介護度の変化と認定率という結果は良好である一方、体制・取組と活動の指標が低いという構造です。</t>
         </is>
       </c>
       <c r="D25" s="9" t="n"/>
@@ -1080,11 +1098,55 @@
         </is>
       </c>
     </row>
-    <row r="27" ht="56" customHeight="1">
-      <c r="A27" s="13" t="inlineStr">
+    <row r="26" ht="76" customHeight="1">
+      <c r="A26" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="B26" s="6" t="inlineStr">
+        <is>
+          <t>評価の対象年度が確定した</t>
+        </is>
+      </c>
+      <c r="C26" s="6" t="inlineStr">
+        <is>
+          <t>令和8年度交付金は令和7年度に実施した取組を評価しています。第9期（令和6〜8年度）の取組のうち、交付金で外部評価されているのは令和5〜7年度の取組です。令和8年度の取組は令和9年度交付金で評価されるため、第9期の最終年度の取組は本計画の策定時には評価結果が出ません。</t>
+        </is>
+      </c>
+      <c r="D26" s="9" t="n"/>
+      <c r="E26" s="10" t="n"/>
+      <c r="F26" s="12" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="76" customHeight="1">
+      <c r="A27" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="B27" s="6" t="inlineStr">
+        <is>
+          <t>成果指向型配分枠が新設された</t>
+        </is>
+      </c>
+      <c r="C27" s="6" t="inlineStr">
+        <is>
+          <t>令和8年度から、成果指向型の介護予防・健康づくりの取組を100点満点で評価する枠が新設されました。地域のデータ分析に基づき、対象層・アウトプット指標・アウトカム指標と目標値を設定することが要件です。第10期の施策設計に直接関わります（06シート）。</t>
+        </is>
+      </c>
+      <c r="D27" s="9" t="n"/>
+      <c r="E27" s="10" t="n"/>
+      <c r="F27" s="11" t="inlineStr">
+        <is>
+          <t>大</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="56" customHeight="1">
+      <c r="A29" s="13" t="inlineStr">
         <is>
           <t>注1）全国集計は集計値のみを収録し、個々の市町村の得点は収録していません（3町分を除く）。
-注2）集計対象は令和6年度1,745団体・令和7年度1,745団体・令和8年度1,746団体です。合計行及び推進・支援合計が800点を超える行は除いています。
+注2）集計対象は令和6年度1,741団体・令和7年度1,741団体・令和8年度1,741団体です。合計行及び推進・支援合計が800点を超える行は除いています。
 注3）PDFは同一のファイルが2件添付されていました。内容はいずれも令和8年度評価指標（市町村分）42頁です。</t>
         </is>
       </c>
@@ -1093,20 +1155,681 @@
   <mergeCells count="16">
     <mergeCell ref="C16:E16"/>
     <mergeCell ref="A2:F2"/>
-    <mergeCell ref="A11:F11"/>
-    <mergeCell ref="C14:E14"/>
-    <mergeCell ref="C13:E13"/>
-    <mergeCell ref="A19:F19"/>
+    <mergeCell ref="C27:E27"/>
+    <mergeCell ref="C19:E19"/>
+    <mergeCell ref="A13:F13"/>
     <mergeCell ref="A1:F1"/>
     <mergeCell ref="C23:E23"/>
-    <mergeCell ref="C22:E22"/>
-    <mergeCell ref="A27:F27"/>
+    <mergeCell ref="C18:E18"/>
     <mergeCell ref="C17:E17"/>
+    <mergeCell ref="C26:E26"/>
     <mergeCell ref="A4:F4"/>
-    <mergeCell ref="C21:E21"/>
+    <mergeCell ref="A21:F21"/>
     <mergeCell ref="C15:E15"/>
+    <mergeCell ref="A29:F29"/>
     <mergeCell ref="C25:E25"/>
     <mergeCell ref="C24:E24"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F36"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="18" customWidth="1" min="1" max="1"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="10" customWidth="1" min="3" max="3"/>
+    <col width="8" customWidth="1" min="4" max="4"/>
+    <col width="8" customWidth="1" min="5" max="5"/>
+    <col width="34" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="26" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>北海道の評価のうち管内市町村の状況で決まる項目</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="60" customHeight="1">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>都道府県分の評価指標には、管内市町村の得点や市町村間の差で決まる項目があります。当広域連合の構成3町の得点は、北海道の得点に影響します。北海道が0点となっている項目のうち、3町が関係するものを確かめました。</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="18" customHeight="1">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>【1　北海道が0点の項目（管内市町村の状況で決まるもの）】</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="32" customHeight="1">
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>目標</t>
+        </is>
+      </c>
+      <c r="B5" s="4" t="inlineStr">
+        <is>
+          <t>大項目</t>
+        </is>
+      </c>
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>枝番</t>
+        </is>
+      </c>
+      <c r="D5" s="4" t="inlineStr">
+        <is>
+          <t>配点</t>
+        </is>
+      </c>
+      <c r="E5" s="4" t="inlineStr">
+        <is>
+          <t>北海道</t>
+        </is>
+      </c>
+      <c r="F5" s="4" t="inlineStr">
+        <is>
+          <t>内容</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="32" customHeight="1">
+      <c r="A6" s="6" t="inlineStr">
+        <is>
+          <t>推進 目標Ⅰ（ⅰ）</t>
+        </is>
+      </c>
+      <c r="B6" s="6" t="inlineStr">
+        <is>
+          <t>2 評価結果の活用</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="inlineStr">
+        <is>
+          <t>オ</t>
+        </is>
+      </c>
+      <c r="D6" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="E6" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="F6" s="6" t="inlineStr">
+        <is>
+          <t>今年度の評価結果において管内に著しく得点の低い市町村がない（全国該当率53.2％）</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="32" customHeight="1">
+      <c r="A7" s="6" t="inlineStr">
+        <is>
+          <t>推進 目標Ⅰ（ⅱ）</t>
+        </is>
+      </c>
+      <c r="B7" s="6" t="inlineStr">
+        <is>
+          <t>2 管内市町村平均点</t>
+        </is>
+      </c>
+      <c r="C7" s="5" t="inlineStr">
+        <is>
+          <t>ア（上位7割）</t>
+        </is>
+      </c>
+      <c r="D7" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="E7" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="F7" s="6" t="inlineStr">
+        <is>
+          <t>管内市町村全体の令和8年度評価得点の平均の全国順位（全国該当率68.1％）</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="32" customHeight="1">
+      <c r="A8" s="6" t="inlineStr">
+        <is>
+          <t>推進 目標Ⅰ（ⅱ）</t>
+        </is>
+      </c>
+      <c r="B8" s="6" t="inlineStr">
+        <is>
+          <t>2 管内市町村平均点</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="inlineStr">
+        <is>
+          <t>イ（上位5割）</t>
+        </is>
+      </c>
+      <c r="D8" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="E8" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="F8" s="6" t="inlineStr">
+        <is>
+          <t>同上（全国該当率48.9％）</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="32" customHeight="1">
+      <c r="A9" s="6" t="inlineStr">
+        <is>
+          <t>推進 目標Ⅰ（ⅱ）</t>
+        </is>
+      </c>
+      <c r="B9" s="6" t="inlineStr">
+        <is>
+          <t>2 管内市町村平均点</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="inlineStr">
+        <is>
+          <t>ウ（上位3割）</t>
+        </is>
+      </c>
+      <c r="D9" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="E9" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="F9" s="6" t="inlineStr">
+        <is>
+          <t>同上（全国該当率29.8％）</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="32" customHeight="1">
+      <c r="A10" s="6" t="inlineStr">
+        <is>
+          <t>推進 目標Ⅰ（ⅱ）</t>
+        </is>
+      </c>
+      <c r="B10" s="6" t="inlineStr">
+        <is>
+          <t>2 管内市町村平均点</t>
+        </is>
+      </c>
+      <c r="C10" s="5" t="inlineStr">
+        <is>
+          <t>エ（上位1割）</t>
+        </is>
+      </c>
+      <c r="D10" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="E10" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="F10" s="6" t="inlineStr">
+        <is>
+          <t>同上（全国該当率8.5％）</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="18" customHeight="1">
+      <c r="A12" s="3" t="inlineStr">
+        <is>
+          <t>【2　「著しく得点の低い市町村」の判定】</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="32" customHeight="1">
+      <c r="A13" s="6" t="inlineStr">
+        <is>
+          <t>定義</t>
+        </is>
+      </c>
+      <c r="B13" s="6" t="inlineStr">
+        <is>
+          <t>令和8年度評価結果の得点率の平均から標準偏差の2倍を差し引いて得た数を下回る市町村</t>
+        </is>
+      </c>
+      <c r="C13" s="9" t="n"/>
+      <c r="D13" s="9" t="n"/>
+      <c r="E13" s="10" t="n"/>
+      <c r="F13" s="6" t="inlineStr">
+        <is>
+          <t>評価指標の留意点による</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="32" customHeight="1">
+      <c r="A14" s="4" t="inlineStr">
+        <is>
+          <t>項目</t>
+        </is>
+      </c>
+      <c r="B14" s="4" t="inlineStr">
+        <is>
+          <t>値</t>
+        </is>
+      </c>
+      <c r="C14" s="4" t="inlineStr"/>
+      <c r="D14" s="4" t="inlineStr"/>
+      <c r="E14" s="4" t="inlineStr"/>
+      <c r="F14" s="4" t="inlineStr">
+        <is>
+          <t>見方</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="24" customHeight="1">
+      <c r="A15" s="6" t="inlineStr">
+        <is>
+          <t>集計対象</t>
+        </is>
+      </c>
+      <c r="B15" s="6" t="inlineStr">
+        <is>
+          <t>1741市町村</t>
+        </is>
+      </c>
+      <c r="C15" s="9" t="n"/>
+      <c r="D15" s="9" t="n"/>
+      <c r="E15" s="10" t="n"/>
+      <c r="F15" s="6" t="inlineStr">
+        <is>
+          <t>市町村分の全国集計による</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="24" customHeight="1">
+      <c r="A16" s="6" t="inlineStr">
+        <is>
+          <t>得点率の平均</t>
+        </is>
+      </c>
+      <c r="B16" s="6" t="inlineStr">
+        <is>
+          <t>0.5689（455.1点）</t>
+        </is>
+      </c>
+      <c r="C16" s="9" t="n"/>
+      <c r="D16" s="9" t="n"/>
+      <c r="E16" s="10" t="n"/>
+      <c r="F16" s="6" t="inlineStr">
+        <is>
+          <t>455.1÷800</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="24" customHeight="1">
+      <c r="A17" s="6" t="inlineStr">
+        <is>
+          <t>標準偏差</t>
+        </is>
+      </c>
+      <c r="B17" s="6" t="inlineStr">
+        <is>
+          <t>0.1096（87.7点）</t>
+        </is>
+      </c>
+      <c r="C17" s="9" t="n"/>
+      <c r="D17" s="9" t="n"/>
+      <c r="E17" s="10" t="n"/>
+      <c r="F17" s="6" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="24" customHeight="1">
+      <c r="A18" s="6" t="inlineStr">
+        <is>
+          <t>閾値</t>
+        </is>
+      </c>
+      <c r="B18" s="6" t="inlineStr">
+        <is>
+          <t>0.3497（279.7点）</t>
+        </is>
+      </c>
+      <c r="C18" s="9" t="n"/>
+      <c r="D18" s="9" t="n"/>
+      <c r="E18" s="10" t="n"/>
+      <c r="F18" s="6" t="inlineStr">
+        <is>
+          <t>平均−2×標準偏差</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="24" customHeight="1">
+      <c r="A19" s="6" t="inlineStr">
+        <is>
+          <t>全国で下回る市町村</t>
+        </is>
+      </c>
+      <c r="B19" s="6" t="inlineStr">
+        <is>
+          <t>55市町村</t>
+        </is>
+      </c>
+      <c r="C19" s="9" t="n"/>
+      <c r="D19" s="9" t="n"/>
+      <c r="E19" s="10" t="n"/>
+      <c r="F19" s="6" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="24" customHeight="1">
+      <c r="A20" s="6" t="inlineStr">
+        <is>
+          <t>北海道で下回る市町村</t>
+        </is>
+      </c>
+      <c r="B20" s="6" t="inlineStr">
+        <is>
+          <t>11市町村</t>
+        </is>
+      </c>
+      <c r="C20" s="9" t="n"/>
+      <c r="D20" s="9" t="n"/>
+      <c r="E20" s="10" t="n"/>
+      <c r="F20" s="6" t="inlineStr">
+        <is>
+          <t>このため北海道は当該項目が0点となっている</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="18" customHeight="1">
+      <c r="A22" s="3" t="inlineStr">
+        <is>
+          <t>【3　構成3町は該当しない】</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="32" customHeight="1">
+      <c r="A23" s="4" t="inlineStr">
+        <is>
+          <t>町</t>
+        </is>
+      </c>
+      <c r="B23" s="4" t="inlineStr">
+        <is>
+          <t>推進・支援合計</t>
+        </is>
+      </c>
+      <c r="C23" s="4" t="inlineStr">
+        <is>
+          <t>得点率</t>
+        </is>
+      </c>
+      <c r="D23" s="4" t="inlineStr">
+        <is>
+          <t>閾値との差</t>
+        </is>
+      </c>
+      <c r="E23" s="4" t="inlineStr"/>
+      <c r="F23" s="4" t="inlineStr">
+        <is>
+          <t>判定</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="24" customHeight="1">
+      <c r="A24" s="6" t="inlineStr">
+        <is>
+          <t>東川町</t>
+        </is>
+      </c>
+      <c r="B24" s="5" t="inlineStr">
+        <is>
+          <t>315点</t>
+        </is>
+      </c>
+      <c r="C24" s="5" t="inlineStr">
+        <is>
+          <t>39.4％</t>
+        </is>
+      </c>
+      <c r="D24" s="5" t="inlineStr">
+        <is>
+          <t>+35.3点</t>
+        </is>
+      </c>
+      <c r="E24" s="6" t="inlineStr"/>
+      <c r="F24" s="8" t="inlineStr">
+        <is>
+          <t>該当しない</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="24" customHeight="1">
+      <c r="A25" s="6" t="inlineStr">
+        <is>
+          <t>美瑛町</t>
+        </is>
+      </c>
+      <c r="B25" s="5" t="inlineStr">
+        <is>
+          <t>308点</t>
+        </is>
+      </c>
+      <c r="C25" s="5" t="inlineStr">
+        <is>
+          <t>38.5％</t>
+        </is>
+      </c>
+      <c r="D25" s="5" t="inlineStr">
+        <is>
+          <t>+28.3点</t>
+        </is>
+      </c>
+      <c r="E25" s="6" t="inlineStr"/>
+      <c r="F25" s="8" t="inlineStr">
+        <is>
+          <t>該当しない</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="24" customHeight="1">
+      <c r="A26" s="6" t="inlineStr">
+        <is>
+          <t>東神楽町</t>
+        </is>
+      </c>
+      <c r="B26" s="5" t="inlineStr">
+        <is>
+          <t>379点</t>
+        </is>
+      </c>
+      <c r="C26" s="5" t="inlineStr">
+        <is>
+          <t>47.4％</t>
+        </is>
+      </c>
+      <c r="D26" s="5" t="inlineStr">
+        <is>
+          <t>+99.3点</t>
+        </is>
+      </c>
+      <c r="E26" s="6" t="inlineStr"/>
+      <c r="F26" s="8" t="inlineStr">
+        <is>
+          <t>該当しない</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="18" customHeight="1">
+      <c r="A28" s="3" t="inlineStr">
+        <is>
+          <t>【4　管内市町村平均点】</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="32" customHeight="1">
+      <c r="A29" s="4" t="inlineStr">
+        <is>
+          <t>項目</t>
+        </is>
+      </c>
+      <c r="B29" s="4" t="inlineStr">
+        <is>
+          <t>値</t>
+        </is>
+      </c>
+      <c r="C29" s="4" t="inlineStr"/>
+      <c r="D29" s="4" t="inlineStr"/>
+      <c r="E29" s="4" t="inlineStr"/>
+      <c r="F29" s="4" t="inlineStr">
+        <is>
+          <t>見方</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="26" customHeight="1">
+      <c r="A30" s="6" t="inlineStr">
+        <is>
+          <t>北海道の管内市町村数</t>
+        </is>
+      </c>
+      <c r="B30" s="6" t="inlineStr">
+        <is>
+          <t>179市町村</t>
+        </is>
+      </c>
+      <c r="C30" s="9" t="n"/>
+      <c r="D30" s="9" t="n"/>
+      <c r="E30" s="10" t="n"/>
+      <c r="F30" s="6" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="26" customHeight="1">
+      <c r="A31" s="6" t="inlineStr">
+        <is>
+          <t>北海道の管内市町村平均</t>
+        </is>
+      </c>
+      <c r="B31" s="6" t="inlineStr">
+        <is>
+          <t>432.58点</t>
+        </is>
+      </c>
+      <c r="C31" s="9" t="n"/>
+      <c r="D31" s="9" t="n"/>
+      <c r="E31" s="10" t="n"/>
+      <c r="F31" s="6" t="inlineStr">
+        <is>
+          <t>市町村分の全国集計から受託者が算定</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="26" customHeight="1">
+      <c r="A32" s="6" t="inlineStr">
+        <is>
+          <t>全国の市町村平均</t>
+        </is>
+      </c>
+      <c r="B32" s="6" t="inlineStr">
+        <is>
+          <t>455.13点</t>
+        </is>
+      </c>
+      <c r="C32" s="9" t="n"/>
+      <c r="D32" s="9" t="n"/>
+      <c r="E32" s="10" t="n"/>
+      <c r="F32" s="6" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="26" customHeight="1">
+      <c r="A33" s="6" t="inlineStr">
+        <is>
+          <t>都道府県別の順位</t>
+        </is>
+      </c>
+      <c r="B33" s="6" t="inlineStr">
+        <is>
+          <t>35位／47</t>
+        </is>
+      </c>
+      <c r="C33" s="9" t="n"/>
+      <c r="D33" s="9" t="n"/>
+      <c r="E33" s="10" t="n"/>
+      <c r="F33" s="6" t="inlineStr">
+        <is>
+          <t>上位74.5％。上位7割に入らないため北海道は0点</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="26" customHeight="1">
+      <c r="A34" s="6" t="inlineStr">
+        <is>
+          <t>3町の位置</t>
+        </is>
+      </c>
+      <c r="B34" s="6" t="inlineStr">
+        <is>
+          <t>東川315・美瑛308・東神楽379</t>
+        </is>
+      </c>
+      <c r="C34" s="9" t="n"/>
+      <c r="D34" s="9" t="n"/>
+      <c r="E34" s="10" t="n"/>
+      <c r="F34" s="6" t="inlineStr">
+        <is>
+          <t>いずれも北海道の管内平均432.58点を下回り、平均を押し下げる側にある</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="72" customHeight="1">
+      <c r="A36" s="13" t="inlineStr">
+        <is>
+          <t>注1）「著しく得点の低い市町村」の閾値及び管内市町村平均は、評価指標の留意点に示された定義に従い、市町村分の全国集計（令和8年度）から受託者が算定したものです。厚生労働省が公表した値ではありません。
+注2）3町はいずれも閾値を上回っており、北海道が当該項目で0点となっていることの原因ではありません。ただし3町はいずれも全国平均（455.13点）及び北海道の管内平均（432.58点）を下回っています。
+注3）都道府県分の評価は北海道が受けるものであり、当広域連合が直接に得点するものではありません。本シートは、北海道の市町村支援の重点がどこに向くかを見るために整理したものです。</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="22">
+    <mergeCell ref="E26"/>
+    <mergeCell ref="B30:E30"/>
+    <mergeCell ref="B15:E15"/>
+    <mergeCell ref="E25"/>
+    <mergeCell ref="B33:E33"/>
+    <mergeCell ref="A12:F12"/>
+    <mergeCell ref="B20:E20"/>
+    <mergeCell ref="B32:E32"/>
+    <mergeCell ref="A2:F2"/>
+    <mergeCell ref="B16:E16"/>
+    <mergeCell ref="A22:F22"/>
+    <mergeCell ref="A4:F4"/>
+    <mergeCell ref="E24"/>
+    <mergeCell ref="B31:E31"/>
+    <mergeCell ref="B18:E18"/>
+    <mergeCell ref="A28:F28"/>
+    <mergeCell ref="B17:E17"/>
+    <mergeCell ref="A36:F36"/>
+    <mergeCell ref="B13:E13"/>
+    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="B19:E19"/>
+    <mergeCell ref="B34:E34"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -9015,7 +9738,7 @@
     <row r="2" ht="60" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>受領した原本により、これまで3町の値しか持たなかった比較を全国1,745〜1,746市町村・北海道179市町村の集計値まで広げました。</t>
+          <t>受領した原本により、これまで3町の値しか持たなかった比較を全国1,741市町村・北海道179市町村の集計値まで広げました。</t>
         </is>
       </c>
     </row>
@@ -9467,7 +10190,7 @@
       <c r="E21" s="6" t="inlineStr"/>
       <c r="F21" s="6" t="inlineStr"/>
       <c r="G21" s="23" t="n">
-        <v>1745</v>
+        <v>1741</v>
       </c>
       <c r="H21" s="6" t="inlineStr">
         <is>
@@ -9499,7 +10222,7 @@
       <c r="E22" s="6" t="inlineStr"/>
       <c r="F22" s="6" t="inlineStr"/>
       <c r="G22" s="23" t="n">
-        <v>1745</v>
+        <v>1741</v>
       </c>
       <c r="H22" s="6" t="inlineStr">
         <is>
@@ -9531,7 +10254,7 @@
       <c r="E23" s="6" t="inlineStr"/>
       <c r="F23" s="6" t="inlineStr"/>
       <c r="G23" s="23" t="n">
-        <v>1746</v>
+        <v>1741</v>
       </c>
       <c r="H23" s="6" t="inlineStr">
         <is>
@@ -11188,4 +11911,640 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F36"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="4" customWidth="1" min="1" max="1"/>
+    <col width="26" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="54" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="26" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>令和8年度評価結果（都道府県分）の受領点検</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="60" customHeight="1">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>令和8年9月25日に都道府県分の2件を受領しました。都道府県分は市町村分とは別の評価であり、本資料に当広域連合及び構成3町の得点はありません（都道府県の行しかありません）。当広域連合の評価は市町村分（令和8年9月2日受領・収録済み）によります。</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="18" customHeight="1">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>【1　受領資料】</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="32" customHeight="1">
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>No.</t>
+        </is>
+      </c>
+      <c r="B5" s="4" t="inlineStr">
+        <is>
+          <t>資料</t>
+        </is>
+      </c>
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>規模</t>
+        </is>
+      </c>
+      <c r="D5" s="4" t="inlineStr">
+        <is>
+          <t>内容</t>
+        </is>
+      </c>
+      <c r="E5" s="4" t="inlineStr">
+        <is>
+          <t>区分</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="40" customHeight="1">
+      <c r="A6" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="B6" s="6" t="inlineStr">
+        <is>
+          <t>令和8年度評価指標（都道府県分）（001732599.pdf）</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="inlineStr">
+        <is>
+          <t>38頁</t>
+        </is>
+      </c>
+      <c r="D6" s="6" t="inlineStr">
+        <is>
+          <t>1 推進交付金400点／2 成果指向型配分枠100点／3 努力支援交付金400点</t>
+        </is>
+      </c>
+      <c r="E6" s="5" t="inlineStr">
+        <is>
+          <t>都道府県分</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="40" customHeight="1">
+      <c r="A7" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="B7" s="6" t="inlineStr">
+        <is>
+          <t>令和8年度 全国集計（都道府県）（001732598.xlsx）</t>
+        </is>
+      </c>
+      <c r="C7" s="5" t="inlineStr">
+        <is>
+          <t>66行×752列</t>
+        </is>
+      </c>
+      <c r="D7" s="6" t="inlineStr">
+        <is>
+          <t>47都道府県の明細列別の得点。推進・支援合計800点満点</t>
+        </is>
+      </c>
+      <c r="E7" s="5" t="inlineStr">
+        <is>
+          <t>都道府県分</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="18" customHeight="1">
+      <c r="A9" s="3" t="inlineStr">
+        <is>
+          <t>【2　市町村分との違い】</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="32" customHeight="1">
+      <c r="A10" s="4" t="inlineStr">
+        <is>
+          <t>区分</t>
+        </is>
+      </c>
+      <c r="B10" s="4" t="inlineStr">
+        <is>
+          <t>都道府県分（今回）</t>
+        </is>
+      </c>
+      <c r="C10" s="4" t="inlineStr">
+        <is>
+          <t>市町村分（令和8年9月2日受領）</t>
+        </is>
+      </c>
+      <c r="D10" s="4" t="inlineStr"/>
+      <c r="E10" s="4" t="inlineStr"/>
+    </row>
+    <row r="11" ht="40" customHeight="1">
+      <c r="A11" s="6" t="inlineStr">
+        <is>
+          <t>評価の対象</t>
+        </is>
+      </c>
+      <c r="B11" s="6" t="inlineStr">
+        <is>
+          <t>47都道府県</t>
+        </is>
+      </c>
+      <c r="C11" s="6" t="inlineStr">
+        <is>
+          <t>1,741市町村</t>
+        </is>
+      </c>
+      <c r="D11" s="9" t="n"/>
+      <c r="E11" s="10" t="n"/>
+    </row>
+    <row r="12" ht="40" customHeight="1">
+      <c r="A12" s="6" t="inlineStr">
+        <is>
+          <t>当広域連合の記載</t>
+        </is>
+      </c>
+      <c r="B12" s="6" t="inlineStr">
+        <is>
+          <t>なし（都道府県の行のみ）</t>
+        </is>
+      </c>
+      <c r="C12" s="6" t="inlineStr">
+        <is>
+          <t>3町それぞれの行に得点。広域連合の行に得点はない</t>
+        </is>
+      </c>
+      <c r="D12" s="9" t="n"/>
+      <c r="E12" s="10" t="n"/>
+    </row>
+    <row r="13" ht="40" customHeight="1">
+      <c r="A13" s="6" t="inlineStr">
+        <is>
+          <t>配点</t>
+        </is>
+      </c>
+      <c r="B13" s="6" t="inlineStr">
+        <is>
+          <t>推進400点＋成果指向型100点＋支援400点</t>
+        </is>
+      </c>
+      <c r="C13" s="6" t="inlineStr">
+        <is>
+          <t>推進400点＋成果指向型100点＋支援400点</t>
+        </is>
+      </c>
+      <c r="D13" s="9" t="n"/>
+      <c r="E13" s="10" t="n"/>
+    </row>
+    <row r="14" ht="40" customHeight="1">
+      <c r="A14" s="6" t="inlineStr">
+        <is>
+          <t>集計表の満点</t>
+        </is>
+      </c>
+      <c r="B14" s="6" t="inlineStr">
+        <is>
+          <t>800点（成果指向型を含まない）</t>
+        </is>
+      </c>
+      <c r="C14" s="6" t="inlineStr">
+        <is>
+          <t>800点（同左）</t>
+        </is>
+      </c>
+      <c r="D14" s="9" t="n"/>
+      <c r="E14" s="10" t="n"/>
+    </row>
+    <row r="15" ht="40" customHeight="1">
+      <c r="A15" s="6" t="inlineStr">
+        <is>
+          <t>目標Ⅱ（努力支援）の中身</t>
+        </is>
+      </c>
+      <c r="B15" s="6" t="inlineStr">
+        <is>
+          <t>計画策定・支援体制の整備・市町村支援／活動指標4項目</t>
+        </is>
+      </c>
+      <c r="C15" s="6" t="inlineStr">
+        <is>
+          <t>サポーター等の地域支援体制・早期診断早期対応・難聴／活動指標3項目</t>
+        </is>
+      </c>
+      <c r="D15" s="9" t="n"/>
+      <c r="E15" s="10" t="n"/>
+    </row>
+    <row r="17" ht="18" customHeight="1">
+      <c r="A17" s="3" t="inlineStr">
+        <is>
+          <t>【3　北海道の得点（都道府県分・令和8年度）】</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="32" customHeight="1">
+      <c r="A18" s="4" t="inlineStr">
+        <is>
+          <t>区分</t>
+        </is>
+      </c>
+      <c r="B18" s="4" t="inlineStr">
+        <is>
+          <t>配点</t>
+        </is>
+      </c>
+      <c r="C18" s="4" t="inlineStr">
+        <is>
+          <t>北海道</t>
+        </is>
+      </c>
+      <c r="D18" s="4" t="inlineStr">
+        <is>
+          <t>全国平均／中央値</t>
+        </is>
+      </c>
+      <c r="E18" s="4" t="inlineStr">
+        <is>
+          <t>見方</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="26" customHeight="1">
+      <c r="A19" s="6" t="inlineStr">
+        <is>
+          <t>推進Ⅰ 持続可能な地域のあるべき姿をかたちにする</t>
+        </is>
+      </c>
+      <c r="B19" s="5" t="n">
+        <v>100</v>
+      </c>
+      <c r="C19" s="8" t="n">
+        <v>72</v>
+      </c>
+      <c r="D19" s="5" t="inlineStr">
+        <is>
+          <t>69.06／70</t>
+        </is>
+      </c>
+      <c r="E19" s="6" t="inlineStr">
+        <is>
+          <t>全国平均を+2.9点</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="26" customHeight="1">
+      <c r="A20" s="6" t="inlineStr">
+        <is>
+          <t>推進Ⅱ 公正・公平な給付を行う体制を構築する</t>
+        </is>
+      </c>
+      <c r="B20" s="5" t="n">
+        <v>100</v>
+      </c>
+      <c r="C20" s="11" t="n">
+        <v>73</v>
+      </c>
+      <c r="D20" s="5" t="inlineStr">
+        <is>
+          <t>76.47／79</t>
+        </is>
+      </c>
+      <c r="E20" s="6" t="inlineStr">
+        <is>
+          <t>全国平均を-3.5点</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="26" customHeight="1">
+      <c r="A21" s="6" t="inlineStr">
+        <is>
+          <t>推進Ⅲ 介護人材の確保その他のサービス提供基盤の整備を推進する</t>
+        </is>
+      </c>
+      <c r="B21" s="5" t="n">
+        <v>100</v>
+      </c>
+      <c r="C21" s="8" t="n">
+        <v>85</v>
+      </c>
+      <c r="D21" s="5" t="inlineStr">
+        <is>
+          <t>77.06／79</t>
+        </is>
+      </c>
+      <c r="E21" s="6" t="inlineStr">
+        <is>
+          <t>全国平均を+7.9点</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="26" customHeight="1">
+      <c r="A22" s="6" t="inlineStr">
+        <is>
+          <t>推進Ⅳ 高齢者がその状況に応じて可能な限り自立した日常生活を営む</t>
+        </is>
+      </c>
+      <c r="B22" s="5" t="n">
+        <v>100</v>
+      </c>
+      <c r="C22" s="8" t="n">
+        <v>60</v>
+      </c>
+      <c r="D22" s="5" t="inlineStr">
+        <is>
+          <t>47.02／45</t>
+        </is>
+      </c>
+      <c r="E22" s="6" t="inlineStr">
+        <is>
+          <t>全国平均を+13.0点</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="26" customHeight="1">
+      <c r="A23" s="6" t="inlineStr">
+        <is>
+          <t>推進合計</t>
+        </is>
+      </c>
+      <c r="B23" s="5" t="n">
+        <v>400</v>
+      </c>
+      <c r="C23" s="8" t="n">
+        <v>290</v>
+      </c>
+      <c r="D23" s="5" t="inlineStr">
+        <is>
+          <t>269.62／273</t>
+        </is>
+      </c>
+      <c r="E23" s="6" t="inlineStr">
+        <is>
+          <t>全国平均を+20.4点</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="26" customHeight="1">
+      <c r="A24" s="6" t="inlineStr">
+        <is>
+          <t>支援Ⅰ 介護予防／日常生活支援を推進する</t>
+        </is>
+      </c>
+      <c r="B24" s="5" t="n">
+        <v>100</v>
+      </c>
+      <c r="C24" s="11" t="n">
+        <v>58</v>
+      </c>
+      <c r="D24" s="5" t="inlineStr">
+        <is>
+          <t>61.98／62</t>
+        </is>
+      </c>
+      <c r="E24" s="6" t="inlineStr">
+        <is>
+          <t>全国平均を-4.0点</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="26" customHeight="1">
+      <c r="A25" s="6" t="inlineStr">
+        <is>
+          <t>支援Ⅱ 認知症総合支援を推進する</t>
+        </is>
+      </c>
+      <c r="B25" s="5" t="n">
+        <v>100</v>
+      </c>
+      <c r="C25" s="11" t="n">
+        <v>70</v>
+      </c>
+      <c r="D25" s="5" t="inlineStr">
+        <is>
+          <t>77.47／78</t>
+        </is>
+      </c>
+      <c r="E25" s="6" t="inlineStr">
+        <is>
+          <t>全国平均を-7.5点</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="26" customHeight="1">
+      <c r="A26" s="6" t="inlineStr">
+        <is>
+          <t>支援Ⅲ 在宅医療・在宅介護連携の体制を構築する</t>
+        </is>
+      </c>
+      <c r="B26" s="5" t="n">
+        <v>100</v>
+      </c>
+      <c r="C26" s="11" t="n">
+        <v>72</v>
+      </c>
+      <c r="D26" s="5" t="inlineStr">
+        <is>
+          <t>79.53／80</t>
+        </is>
+      </c>
+      <c r="E26" s="6" t="inlineStr">
+        <is>
+          <t>全国平均を-7.5点</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="26" customHeight="1">
+      <c r="A27" s="6" t="inlineStr">
+        <is>
+          <t>支援Ⅳ 高齢者がその状況に応じて可能な限り自立した日常生活を営む</t>
+        </is>
+      </c>
+      <c r="B27" s="5" t="n">
+        <v>100</v>
+      </c>
+      <c r="C27" s="8" t="n">
+        <v>60</v>
+      </c>
+      <c r="D27" s="5" t="inlineStr">
+        <is>
+          <t>47.02／45</t>
+        </is>
+      </c>
+      <c r="E27" s="6" t="inlineStr">
+        <is>
+          <t>全国平均を+13.0点</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="26" customHeight="1">
+      <c r="A28" s="6" t="inlineStr">
+        <is>
+          <t>支援合計</t>
+        </is>
+      </c>
+      <c r="B28" s="5" t="n">
+        <v>400</v>
+      </c>
+      <c r="C28" s="11" t="n">
+        <v>260</v>
+      </c>
+      <c r="D28" s="5" t="inlineStr">
+        <is>
+          <t>266.00／267</t>
+        </is>
+      </c>
+      <c r="E28" s="6" t="inlineStr">
+        <is>
+          <t>全国平均を-6.0点</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="26" customHeight="1">
+      <c r="A29" s="6" t="inlineStr">
+        <is>
+          <t>推進・支援合計</t>
+        </is>
+      </c>
+      <c r="B29" s="5" t="n">
+        <v>800</v>
+      </c>
+      <c r="C29" s="8" t="n">
+        <v>550</v>
+      </c>
+      <c r="D29" s="5" t="inlineStr">
+        <is>
+          <t>535.62／534</t>
+        </is>
+      </c>
+      <c r="E29" s="6" t="inlineStr">
+        <is>
+          <t>全国平均を+14.4点</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="18" customHeight="1">
+      <c r="A31" s="3" t="inlineStr">
+        <is>
+          <t>【4　前年度との比較】</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="32" customHeight="1">
+      <c r="A32" s="4" t="inlineStr">
+        <is>
+          <t>年度</t>
+        </is>
+      </c>
+      <c r="B32" s="4" t="inlineStr">
+        <is>
+          <t>北海道の得点</t>
+        </is>
+      </c>
+      <c r="C32" s="4" t="inlineStr">
+        <is>
+          <t>全国順位</t>
+        </is>
+      </c>
+      <c r="D32" s="4" t="inlineStr">
+        <is>
+          <t>全国平均／中央値／標準偏差</t>
+        </is>
+      </c>
+      <c r="E32" s="4" t="inlineStr">
+        <is>
+          <t>見方</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="24" customHeight="1">
+      <c r="A33" s="6" t="inlineStr">
+        <is>
+          <t>令和7年度</t>
+        </is>
+      </c>
+      <c r="B33" s="5" t="inlineStr">
+        <is>
+          <t>570／800点</t>
+        </is>
+      </c>
+      <c r="C33" s="5" t="inlineStr">
+        <is>
+          <t>10位／47</t>
+        </is>
+      </c>
+      <c r="D33" s="5" t="inlineStr">
+        <is>
+          <t>528.79／527／45.36</t>
+        </is>
+      </c>
+      <c r="E33" s="6" t="inlineStr">
+        <is>
+          <t>全国平均を+41.2点</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="24" customHeight="1">
+      <c r="A34" s="6" t="inlineStr">
+        <is>
+          <t>令和8年度</t>
+        </is>
+      </c>
+      <c r="B34" s="5" t="inlineStr">
+        <is>
+          <t>550／800点</t>
+        </is>
+      </c>
+      <c r="C34" s="5" t="inlineStr">
+        <is>
+          <t>19位／47</t>
+        </is>
+      </c>
+      <c r="D34" s="5" t="inlineStr">
+        <is>
+          <t>535.62／534／43.33</t>
+        </is>
+      </c>
+      <c r="E34" s="6" t="inlineStr">
+        <is>
+          <t>全国平均を+14.4点</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="56" customHeight="1">
+      <c r="A36" s="13" t="inlineStr">
+        <is>
+          <t>注）北海道は令和7年度570点・全国10位から、令和8年度550点・全国19位となりました。全国平均は528.79点から535.62点へ上がっており、得点が下がった一方で全国は上がったため順位が9つ下がっています。得点自体は全国平均を14.4点上回っています。</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="12">
+    <mergeCell ref="A2:F2"/>
+    <mergeCell ref="A4:E4"/>
+    <mergeCell ref="C11:E11"/>
+    <mergeCell ref="C14:E14"/>
+    <mergeCell ref="C13:E13"/>
+    <mergeCell ref="A17:E17"/>
+    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="C15:E15"/>
+    <mergeCell ref="A36:E36"/>
+    <mergeCell ref="A31:E31"/>
+    <mergeCell ref="C12:E12"/>
+    <mergeCell ref="A9:E9"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/output/第10期計画_交付金評価指標と全国集計の受領点検.xlsx
+++ b/output/第10期計画_交付金評価指標と全国集計の受領点検.xlsx
@@ -902,7 +902,7 @@
       </c>
       <c r="C15" s="6" t="inlineStr">
         <is>
-          <t>3町×3か年×22項目の198値をすべて突合しました。不一致は0件です。data_kofukin.py の収録値は原本と一致しています。</t>
+          <t>3町×3か年×22項目の198値をすべて突合しました。不一致は0件です。当方の収録値は原本と一致しています。</t>
         </is>
       </c>
       <c r="D15" s="9" t="n"/>
@@ -1863,7 +1863,7 @@
     <row r="2" ht="60" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>data_kofukin.py に収録している3町×3か年の得点を、受領した原本と1件ずつ突合しました。</t>
+          <t>当方が収録している3町×3か年の得点を、受領した原本と1件ずつ突合しました。</t>
         </is>
       </c>
     </row>
@@ -9636,7 +9636,7 @@
       <c r="F23" s="10" t="n"/>
       <c r="G23" s="6" t="inlineStr">
         <is>
-          <t>data_kofukin_item.py の説明を、受領したPDFにより裏づけた。同モジュールは既に「ITEM の配点は達成度の分母としては用いない」としている</t>
+          <t>配点についての当方の整理を、受領したPDFにより裏づけた。当方は既に「配点は達成度の分母としては用いない」としている</t>
         </is>
       </c>
     </row>
@@ -11739,7 +11739,7 @@
       </c>
       <c r="B12" s="6" t="inlineStr">
         <is>
-          <t>data_kofukin_zenkoku.py</t>
+          <t>全国集計の収録値</t>
         </is>
       </c>
       <c r="C12" s="6" t="inlineStr">
